--- a/assets/files/quotes/ZK08-quotation.xlsx
+++ b/assets/files/quotes/ZK08-quotation.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>人民币（RMB）参考价；最终以双方确认采购清单为准</t>
+          <t>人民币（RMB）参考价；最终价格以双方签署的合同价格为准</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr"/>
@@ -1235,6 +1235,20 @@
       </c>
       <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>报价说明</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>页面与本表报价均为参考资料，最终价格以双方签署的合同价格为准。</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/assets/files/quotes/ZK08-quotation.xlsx
+++ b/assets/files/quotes/ZK08-quotation.xlsx
@@ -7,17 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="报价单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文报价单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English Quotation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中文报价单'!$A$8:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'English Quotation'!$A$8:$D$41</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="¥#,##0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +32,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="000B1220"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="0053657E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -49,7 +68,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F4F8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00126BFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,16 +108,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,18 +497,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ZK08 应急指挥舱 报价单</t>
@@ -475,785 +519,1292 @@
       <c r="D1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>公司</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>中科国际 Zhongke International</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>地址</t>
+          <t>公司 / Company</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>香港尖沙咀麼地道75号南洋中心2座7楼</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+          <t>中科国际 Zhongke International</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>联系人</t>
+          <t>地址 / Address</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>杨涛峰 / 13319274381</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+          <t>香港尖沙咀麼地道75号南洋中心2座7楼</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>币种</t>
+          <t>联系人 / Contact</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>人民币（RMB）参考价；最终价格以双方签署的合同价格为准</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="3" t="inlineStr"/>
-      <c r="B6" s="3" t="inlineStr"/>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>杨涛峰 / 13319274381</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>币种 / Currency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>人民币（RMB）参考价</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>价格说明 / Price Note</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>最终价格以双方签署的合同价格为准</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>价格（人民币，参考）</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>参考价格</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>ZK08 应急指挥舱</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>项目定制报价模板，价格待项目确认</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>项目确认</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>项目定制型号，价格需以项目方案和采购清单确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="2" t="inlineStr"/>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>以项目方案确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>可选配置</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>参考价格</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>勾选/确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>全套卫浴 / 带洗浴</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>储物柜（衣物收纳）</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>床及床垫（单套）</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>9300</v>
+          <t>全套卫浴 / 带洗浴</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="7" t="n">
+        <v>25000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>第二床位 / 第二床垫</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>储物柜（衣物收纳）</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>桌椅套装（等级及数量按采购确认）</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>2500</v>
+          <t>床及床垫（单套）</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="7" t="n">
+        <v>9300</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>电器包（电视机、冰箱、微波炉、烤箱等）</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>第二床位 / 第二床垫</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="8" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>电动窗帘</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>5700</v>
+          <t>桌椅套装（等级及数量按采购确认）</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="7" t="n">
+        <v>2500</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Low-E 玻璃升级</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>电器包（电视机、冰箱、微波炉、烤箱等）</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>天窗</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>15000</v>
+          <t>电动窗帘</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="7" t="n">
+        <v>5700</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>内饰升级包</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>40000</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Low-E 玻璃升级</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>地暖系统</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>20000</v>
+          <t>天窗</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="7" t="n">
+        <v>15000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>灯带 / 氛围照明系统</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>内饰升级包</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>中央空调</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="n">
-        <v>40000</v>
+          <t>地暖系统</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="7" t="n">
+        <v>20000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>挂机空调</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>4700</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>灯带 / 氛围照明系统</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>新风系统</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>15000</v>
+          <t>中央空调</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="7" t="n">
+        <v>40000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>顶部太阳能光伏板（约3kW，含支架及布线辅材）</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>挂机空调</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="8" t="n">
+        <v>4700</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>储能电池系统（约10kWh，含BMS及安装辅材）</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="n">
-        <v>50000</v>
+          <t>新风系统</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="7" t="n">
+        <v>15000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>逆变器 / 能源管理系统</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>顶部太阳能光伏板（约3kW，含支架及布线辅材）</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>星链连接硬件及安装辅材（月费另计，按当地套餐执行）</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="n">
-        <v>33200</v>
+          <t>储能电池系统（约10kWh，含BMS及安装辅材）</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="7" t="n">
+        <v>50000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>国际通信系统（WiFi / GPS / 北斗）</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n">
-        <v>10800</v>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>逆变器 / 能源管理系统</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LED 大屏幕</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="n">
-        <v>28000</v>
+          <t>星链连接硬件及安装辅材（月费另计，按当地套餐执行）</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="7" t="n">
+        <v>33200</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>投影仪</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n">
-        <v>5800</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>国际通信系统（WiFi / GPS / 北斗）</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>3D 展示系统</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="n">
-        <v>25000</v>
+          <t>LED 大屏幕</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="7" t="n">
+        <v>28000</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>AI 智能全系统（前台 / 后台 / 数据中心基础版）</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>投影仪</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AI 语音控制 / 设备联动全屋智能</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>20000</v>
+          <t>3D 展示系统</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="7" t="n">
+        <v>25000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>净水系统（RO / 过滤 / 水泵，按最终方案确认）</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>AI 智能全系统（前台 / 后台 / 数据中心基础版）</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>智能门锁</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>1600</v>
+          <t>AI 语音控制 / 设备联动全屋智能</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="7" t="n">
+        <v>20000</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>监控 / 烟感 / 水浸报警基础包</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>4700</v>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>□</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>净水系统（RO / 过滤 / 水泵，按最终方案确认）</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>运输成本合计（参考，按路线、港口、安装条件确认）</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>按项目实际配置确认</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>96700</v>
+          <t>智能门锁</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="7" t="n">
+        <v>1600</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>□</t>
+          <t>可选</t>
         </is>
       </c>
     </row>
     <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="2" t="inlineStr"/>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>监控 / 烟感 / 水浸报警基础包</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="8" t="n">
+        <v>4700</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>报价说明</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>本报价单为官网公开参考文件，不含税费、关税、当地认证、现场土建及特殊运输安装条件。</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>报价说明</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>医疗、通信、无人机、星链等涉及当地许可或服务月费的项目需另行确认。</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>报价说明</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>原 ZK01-05 表格中的 ZK05 为“移动拖车版”附加项，不作为当前 ZK05 露台舱价格。</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>报价说明</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>页面与本表报价均为参考资料，最终价格以双方签署的合同价格为准。</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>运输成本合计（参考，按路线、港口、安装条件确认）</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="7" t="n">
+        <v>96700</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <autoFilter ref="A8:D41"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ZK08 Emergency Command Capsule Quotation</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr"/>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>公司 / Company</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>中科国际 Zhongke International</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>地址 / Address</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>香港尖沙咀麼地道75号南洋中心2座7楼</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>联系人 / Contact</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>杨涛峰 / 13319274381</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>币种 / Currency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>RMB reference price</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>价格说明 / Price Note</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Final price is subject to the signed contract</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Reference Price</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ZK08 Emergency Command Capsule</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Customized project quotation template; price to be confirmed by project</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Project confirmation</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Subject to project proposal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Optional Configuration</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Reference Price</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Complete bathroom / shower</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Storage cabinet / wardrobe</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr"/>
+      <c r="C14" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Bed and mattress set</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="7" t="n">
+        <v>9300</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Second bed / second mattress</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="8" t="n">
+        <v>3200</v>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Desk and chair set, grade and quantity to be confirmed</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Appliance package: TV, refrigerator, microwave, oven, etc.</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Motorized curtains</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="7" t="n">
+        <v>5700</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Low-E glass upgrade</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Skylight</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Interior finish upgrade package</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="8" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Floor heating system</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Light strip / ambient lighting system</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Central air conditioning</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="7" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Wall-mounted air conditioner</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr"/>
+      <c r="C26" s="8" t="n">
+        <v>4700</v>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Fresh air ventilation system</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Roof solar PV panels, approx. 3kW including brackets and wiring accessories</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Energy storage battery system, approx. 10kWh including BMS and installation accessories</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Inverter / energy management system</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Starlink hardware and installation accessories; monthly fee excluded</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="7" t="n">
+        <v>33200</v>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>International communication system: WiFi / GPS / BeiDou</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>LED display screen</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="7" t="n">
+        <v>28000</v>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Projector</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="8" t="n">
+        <v>5800</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>3D presentation system</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>AI smart system, basic front desk / backend / data center version</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>AI voice control / device-linked smart system</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Water purification system: RO / filter / pump, subject to final plan</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Smart door lock</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="7" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Basic security package: camera / smoke alarm / water leak alarm</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="8" t="n">
+        <v>4700</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Estimated logistics cost, subject to route, port and installation conditions</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="7" t="n">
+        <v>96700</v>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A8:D41"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/assets/files/quotes/ZK08-quotation.xlsx
+++ b/assets/files/quotes/ZK08-quotation.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="English Quotation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中文报价单'!$A$11:$E$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'English Quotation'!$A$11:$E$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'中文报价单'!$A$11:$E$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'English Quotation'!$A$11:$E$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -631,9 +631,11 @@
       <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="6" t="n"/>
+      <c r="A6" s="6" t="n">
+        <v>1500000</v>
+      </c>
       <c r="B6" s="6">
-        <f>IF(SUM(D12:D40)=0,"",SUM(D12:D40))</f>
+        <f>IF(SUM(D12:D45)=0,"",SUM(D12:D45))</f>
         <v/>
       </c>
       <c r="C6" s="6">
@@ -679,12 +681,14 @@
           <t>ZK08 应急指挥舱</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>1500000</v>
+      </c>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>项目定制</t>
+          <t>高规格应急系统基础配置，含应急通信、备用电源、指挥调度和警示识别能力</t>
         </is>
       </c>
     </row>
@@ -725,11 +729,11 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>全套卫浴 / 带洗浴</t>
+          <t>卫星通信增强包</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>25000</v>
+        <v>120000</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
@@ -740,16 +744,20 @@
         <f>IF($C12="☑",$B12,"")</f>
         <v/>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>在基础应急通信上增加卫星/多链路冗余</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>储物柜（衣物收纳）</t>
+          <t>大型地图指挥屏增强包</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>7000</v>
+        <v>80000</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -760,16 +768,20 @@
         <f>IF($C13="☑",$B13,"")</f>
         <v/>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>地图大屏、指挥显示和多源画面接入</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>床及床垫（单套）</t>
+          <t>便携应急医疗包</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>9300</v>
+        <v>60000</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
@@ -780,16 +792,20 @@
         <f>IF($C14="☑",$B14,"")</f>
         <v/>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>基础救援、急救和应急医疗物资配置</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>第二床位 / 第二床垫</t>
+          <t>无人机指挥 / 充电接口</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>3200</v>
+        <v>90000</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
@@ -800,16 +816,20 @@
         <f>IF($C15="☑",$B15,"")</f>
         <v/>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>无人机起降、充电和应急巡检接口</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>桌椅套装</t>
+          <t>额外储能 / 发电机接口</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>2500</v>
+        <v>150000</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
@@ -820,16 +840,20 @@
         <f>IF($C16="☑",$B16,"")</f>
         <v/>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>高规格备用电源和外接发电机接口增强</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>电器包</t>
+          <t>全套卫浴 / 带洗浴</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
@@ -845,11 +869,11 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>电动窗帘</t>
+          <t>储物柜（衣物收纳）</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>5700</v>
+        <v>7000</v>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
@@ -865,11 +889,11 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Low-E 玻璃升级</t>
+          <t>床及床垫（单套）</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>20000</v>
+        <v>9300</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
@@ -885,11 +909,11 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>天窗</t>
+          <t>第二床位 / 第二床垫</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>15000</v>
+        <v>3200</v>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
@@ -905,11 +929,11 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>内饰升级包</t>
+          <t>桌椅套装</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>40000</v>
+        <v>2500</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
@@ -925,11 +949,11 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>地暖系统</t>
+          <t>电器包</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
@@ -945,11 +969,11 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>灯带 / 氛围照明系统</t>
+          <t>电动窗帘</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2500</v>
+        <v>5700</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
@@ -965,11 +989,11 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>中央空调</t>
+          <t>Low-E 玻璃升级</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
@@ -985,11 +1009,11 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>挂机空调</t>
+          <t>天窗</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
@@ -1005,11 +1029,11 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>新风系统</t>
+          <t>内饰升级包</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
@@ -1025,11 +1049,11 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>顶部太阳能光伏板</t>
+          <t>地暖系统</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
@@ -1045,11 +1069,11 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>储能电池系统</t>
+          <t>灯带 / 氛围照明系统</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>50000</v>
+        <v>2500</v>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
@@ -1065,11 +1089,11 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>逆变器 / 能源管理系统</t>
+          <t>中央空调</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
@@ -1085,11 +1109,11 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>星链连接硬件及安装辅材</t>
+          <t>挂机空调</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>33200</v>
+        <v>4700</v>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
@@ -1105,11 +1129,11 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>国际通信系统</t>
+          <t>新风系统</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>10800</v>
+        <v>15000</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
@@ -1125,11 +1149,11 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>LED 大屏幕</t>
+          <t>顶部太阳能光伏板</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
@@ -1145,11 +1169,11 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>投影仪</t>
+          <t>储能电池系统</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>5800</v>
+        <v>50000</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
@@ -1165,11 +1189,11 @@
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3D 展示系统</t>
+          <t>逆变器 / 能源管理系统</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
@@ -1185,11 +1209,11 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AI 智能全系统</t>
+          <t>星链连接硬件及安装辅材</t>
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>100000</v>
+        <v>33200</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
@@ -1205,11 +1229,11 @@
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>AI 语音控制 / 设备联动全屋智能</t>
+          <t>国际通信系统</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>20000</v>
+        <v>10800</v>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
@@ -1225,11 +1249,11 @@
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>净水系统</t>
+          <t>LED 大屏幕</t>
         </is>
       </c>
       <c r="B37" s="9" t="n">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
@@ -1245,11 +1269,11 @@
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>智能门锁</t>
+          <t>投影仪</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>1600</v>
+        <v>5800</v>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
@@ -1265,11 +1289,11 @@
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>监控 / 烟感 / 水浸报警基础包</t>
+          <t>3D 展示系统</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>4700</v>
+        <v>25000</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
@@ -1285,11 +1309,11 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>运输成本合计</t>
+          <t>AI 智能全系统</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>96700</v>
+        <v>100000</v>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
@@ -1302,18 +1326,118 @@
       </c>
       <c r="E40" s="4" t="inlineStr"/>
     </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AI 语音控制 / 设备联动全屋智能</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D41" s="9">
+        <f>IF($C41="☑",$B41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>净水系统</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D42" s="10">
+        <f>IF($C42="☑",$B42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>智能门锁</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D43" s="9">
+        <f>IF($C43="☑",$B43,"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>监控 / 烟感 / 水浸报警基础包</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D44" s="10">
+        <f>IF($C44="☑",$B44,"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>运输成本合计</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>96700</v>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D45" s="9">
+        <f>IF($C45="☑",$B45,"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:E40"/>
+  <autoFilter ref="A11:E45"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A12:E40">
+  <conditionalFormatting sqref="A12:E45">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$C12="☑"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C12:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select from the list" promptTitle="Checkbox" prompt="Select checkbox" type="list">
+    <dataValidation sqref="C12:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select from the list" promptTitle="Checkbox" prompt="Select checkbox" type="list">
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1328,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1426,9 +1550,11 @@
       <c r="E5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="6" t="n"/>
+      <c r="A6" s="6" t="n">
+        <v>1500000</v>
+      </c>
       <c r="B6" s="6">
-        <f>IF(SUM(D12:D40)=0,"",SUM(D12:D40))</f>
+        <f>IF(SUM(D12:D45)=0,"",SUM(D12:D45))</f>
         <v/>
       </c>
       <c r="C6" s="6">
@@ -1474,12 +1600,14 @@
           <t>ZK08 Emergency Command Capsule</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
+      <c r="B9" s="9" t="n">
+        <v>1500000</v>
+      </c>
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Customized project</t>
+          <t>High-spec emergency system base configuration with emergency communications, backup power, command dispatch and warning identity</t>
         </is>
       </c>
     </row>
@@ -1520,11 +1648,11 @@
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Complete bathroom / shower</t>
+          <t>Satellite communication enhancement package</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>25000</v>
+        <v>120000</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
@@ -1535,16 +1663,20 @@
         <f>IF($C12="☑",$B12,"")</f>
         <v/>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Adds satellite / multi-link redundancy to the base emergency communication system</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Storage cabinet / wardrobe</t>
+          <t>Large map command display enhancement</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>7000</v>
+        <v>80000</v>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
@@ -1555,16 +1687,20 @@
         <f>IF($C13="☑",$B13,"")</f>
         <v/>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Large map display, command screen and multi-source video access</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Bed and mattress set</t>
+          <t>Portable emergency medical package</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>9300</v>
+        <v>60000</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
@@ -1575,16 +1711,20 @@
         <f>IF($C14="☑",$B14,"")</f>
         <v/>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Basic rescue, first-aid and emergency medical supplies</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Second bed / second mattress</t>
+          <t>Drone command / charging interface</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>3200</v>
+        <v>90000</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
@@ -1595,16 +1735,20 @@
         <f>IF($C15="☑",$B15,"")</f>
         <v/>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Drone landing, charging and emergency inspection interfaces</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Desk and chair set</t>
+          <t>Extra storage / generator interface</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>2500</v>
+        <v>150000</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
@@ -1615,16 +1759,20 @@
         <f>IF($C16="☑",$B16,"")</f>
         <v/>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Enhanced backup power and external generator interface</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Appliance package</t>
+          <t>Complete bathroom / shower</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>40000</v>
+        <v>25000</v>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
@@ -1640,11 +1788,11 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Motorized curtains</t>
+          <t>Storage cabinet / wardrobe</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>5700</v>
+        <v>7000</v>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
@@ -1660,11 +1808,11 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Low-E glass upgrade</t>
+          <t>Bed and mattress set</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>20000</v>
+        <v>9300</v>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
@@ -1680,11 +1828,11 @@
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Skylight</t>
+          <t>Second bed / second mattress</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>15000</v>
+        <v>3200</v>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
@@ -1700,11 +1848,11 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Interior finish upgrade package</t>
+          <t>Desk and chair set</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>40000</v>
+        <v>2500</v>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
@@ -1720,11 +1868,11 @@
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Floor heating system</t>
+          <t>Appliance package</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
@@ -1740,11 +1888,11 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Light strip / ambient lighting system</t>
+          <t>Motorized curtains</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2500</v>
+        <v>5700</v>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
@@ -1760,11 +1908,11 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Central air conditioning</t>
+          <t>Low-E glass upgrade</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
@@ -1780,11 +1928,11 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Wall-mounted air conditioner</t>
+          <t>Skylight</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
@@ -1800,11 +1948,11 @@
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Fresh air ventilation system</t>
+          <t>Interior finish upgrade package</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
@@ -1820,11 +1968,11 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Roof solar PV panels</t>
+          <t>Floor heating system</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
@@ -1840,11 +1988,11 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Energy storage battery system</t>
+          <t>Light strip / ambient lighting system</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>50000</v>
+        <v>2500</v>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
@@ -1860,11 +2008,11 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Inverter / energy management system</t>
+          <t>Central air conditioning</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
@@ -1880,11 +2028,11 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Starlink hardware and installation accessories</t>
+          <t>Wall-mounted air conditioner</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>33200</v>
+        <v>4700</v>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
@@ -1900,11 +2048,11 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>International communication system</t>
+          <t>Fresh air ventilation system</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>10800</v>
+        <v>15000</v>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
@@ -1920,11 +2068,11 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>LED display screen</t>
+          <t>Roof solar PV panels</t>
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
@@ -1940,11 +2088,11 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Projector</t>
+          <t>Energy storage battery system</t>
         </is>
       </c>
       <c r="B33" s="9" t="n">
-        <v>5800</v>
+        <v>50000</v>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
@@ -1960,11 +2108,11 @@
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>3D presentation system</t>
+          <t>Inverter / energy management system</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
@@ -1980,11 +2128,11 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>AI smart system</t>
+          <t>Starlink hardware and installation accessories</t>
         </is>
       </c>
       <c r="B35" s="9" t="n">
-        <v>100000</v>
+        <v>33200</v>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
@@ -2000,11 +2148,11 @@
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>AI voice control / device-linked smart system</t>
+          <t>International communication system</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>20000</v>
+        <v>10800</v>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
@@ -2020,11 +2168,11 @@
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Water purification system</t>
+          <t>LED display screen</t>
         </is>
       </c>
       <c r="B37" s="9" t="n">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
@@ -2040,11 +2188,11 @@
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Smart door lock</t>
+          <t>Projector</t>
         </is>
       </c>
       <c r="B38" s="10" t="n">
-        <v>1600</v>
+        <v>5800</v>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
@@ -2060,11 +2208,11 @@
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Basic security package</t>
+          <t>3D presentation system</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>4700</v>
+        <v>25000</v>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
@@ -2080,11 +2228,11 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Estimated logistics cost</t>
+          <t>AI smart system</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>96700</v>
+        <v>100000</v>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
@@ -2097,18 +2245,118 @@
       </c>
       <c r="E40" s="4" t="inlineStr"/>
     </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>AI voice control / device-linked smart system</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D41" s="9">
+        <f>IF($C41="☑",$B41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Water purification system</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D42" s="10">
+        <f>IF($C42="☑",$B42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Smart door lock</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D43" s="9">
+        <f>IF($C43="☑",$B43,"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Basic security package</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D44" s="10">
+        <f>IF($C44="☑",$B44,"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Estimated logistics cost</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>96700</v>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="D45" s="9">
+        <f>IF($C45="☑",$B45,"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A11:E40"/>
+  <autoFilter ref="A11:E45"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A12:E40">
+  <conditionalFormatting sqref="A12:E45">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$C12="☑"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="C12:C40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select from the list" promptTitle="Checkbox" prompt="Select checkbox" type="list">
+    <dataValidation sqref="C12:C45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Invalid value" error="Please select from the list" promptTitle="Checkbox" prompt="Select checkbox" type="list">
       <formula1>"☐,☑"</formula1>
     </dataValidation>
   </dataValidations>
